--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">無敵</t>
+          <t xml:space="preserve">無敵結界（免疫一切傷害與負面效果）</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊提升</t>
+          <t xml:space="preserve">攻擊</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">防禦提升</t>
+          <t xml:space="preserve">防禦</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻速提升</t>
+          <t xml:space="preserve">攻速</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃避提升</t>
+          <t xml:space="preserve">閃避</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">爆傷提升</t>
+          <t xml:space="preserve">爆傷</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">格擋提升</t>
+          <t xml:space="preserve">格擋</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">反震提升</t>
+          <t xml:space="preserve">反震</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">掉寶提升</t>
+          <t xml:space="preserve">掉寶</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">穿透提升</t>
+          <t xml:space="preserve">物理/魔法穿透</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">所有傷害提升</t>
+          <t xml:space="preserve">時空凝滯·所有傷害</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">極速之力</t>
+          <t xml:space="preserve">極速之力·攻速</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷霆過載</t>
+          <t xml:space="preserve">雷霆過載·雷電傷害</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">時間坍縮</t>
+          <t xml:space="preserve">時間坍縮·冷卻縮減</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖療逆轉</t>
+          <t xml:space="preserve">聖療逆轉·回復/溢傷</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊下降</t>
+          <t xml:space="preserve">攻擊</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">防禦下降</t>
+          <t xml:space="preserve">防禦</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻速下降</t>
+          <t xml:space="preserve">時間結界·攻速</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -736,17 +736,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">atkUp</t>
+          <t xml:space="preserve">shield</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊</t>
+          <t xml:space="preserve">護盾</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚔️</t>
+          <t xml:space="preserve">🛡️</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -756,32 +756,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">stat</t>
+          <t xml:space="preserve">shield</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">atkUp</t>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maxHp</t>
         </is>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
         <v>15</v>
       </c>
-      <c r="M12">
-        <v>6</v>
-      </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">refresh</t>
+          <t xml:space="preserve">strongest</t>
         </is>
       </c>
       <c r="P12">
@@ -789,24 +794,24 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊力提高。</t>
+          <t xml:space="preserve">吸收傷害的屏障，占施法者最大生命一定比例；被打完或時間到就消失（時間到時未用完的部分一併消失）。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">defUp</t>
+          <t xml:space="preserve">atkUp</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">防禦</t>
+          <t xml:space="preserve">攻擊</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">🛡️</t>
+          <t xml:space="preserve">⚔️</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -821,7 +826,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">defUp</t>
+          <t xml:space="preserve">atkUp</t>
         </is>
       </c>
       <c r="I13">
@@ -831,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="M13">
         <v>6</v>
@@ -849,24 +854,24 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t xml:space="preserve">防禦力提高。</t>
+          <t xml:space="preserve">攻擊力提高。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">aspdUp</t>
+          <t xml:space="preserve">defUp</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻速</t>
+          <t xml:space="preserve">防禦</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🛡️</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -881,7 +886,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">aspdUp</t>
+          <t xml:space="preserve">defUp</t>
         </is>
       </c>
       <c r="I14">
@@ -891,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="M14">
         <v>6</v>
@@ -909,24 +914,24 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊速度提高。</t>
+          <t xml:space="preserve">防禦力提高。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">evasionUp</t>
+          <t xml:space="preserve">aspdUp</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃避</t>
+          <t xml:space="preserve">攻速</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -941,7 +946,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">evasionUp</t>
+          <t xml:space="preserve">aspdUp</t>
         </is>
       </c>
       <c r="I15">
@@ -954,7 +959,7 @@
         <v>25</v>
       </c>
       <c r="M15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -969,24 +974,24 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃避提高。</t>
+          <t xml:space="preserve">攻擊速度提高。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">critDmgUp</t>
+          <t xml:space="preserve">evasionUp</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">爆傷</t>
+          <t xml:space="preserve">閃避</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">💥</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1001,7 +1006,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">critDmgUp</t>
+          <t xml:space="preserve">evasionUp</t>
         </is>
       </c>
       <c r="I16">
@@ -1011,10 +1016,10 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -1029,24 +1034,24 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t xml:space="preserve">爆擊傷害提高。</t>
+          <t xml:space="preserve">閃避提高。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">blockUp</t>
+          <t xml:space="preserve">critDmgUp</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">格擋</t>
+          <t xml:space="preserve">爆傷</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔰</t>
+          <t xml:space="preserve">💥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1061,7 +1066,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">blockUp</t>
+          <t xml:space="preserve">critDmgUp</t>
         </is>
       </c>
       <c r="I17">
@@ -1071,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="M17">
         <v>6</v>
@@ -1089,24 +1094,24 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t xml:space="preserve">格擋率提高。</t>
+          <t xml:space="preserve">爆擊傷害提高。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">thornsUp</t>
+          <t xml:space="preserve">blockUp</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">反震</t>
+          <t xml:space="preserve">格擋</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌵</t>
+          <t xml:space="preserve">🔰</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1121,7 +1126,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">thornsUp</t>
+          <t xml:space="preserve">blockUp</t>
         </is>
       </c>
       <c r="I18">
@@ -1131,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -1149,24 +1154,24 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t xml:space="preserve">反震傷害提高。</t>
+          <t xml:space="preserve">格擋率提高。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">lootUp</t>
+          <t xml:space="preserve">thornsUp</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">掉寶</t>
+          <t xml:space="preserve">反震</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">🎁</t>
+          <t xml:space="preserve">🌵</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1181,7 +1186,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">lootUp</t>
+          <t xml:space="preserve">thornsUp</t>
         </is>
       </c>
       <c r="I19">
@@ -1194,7 +1199,7 @@
         <v>15</v>
       </c>
       <c r="M19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -1209,24 +1214,24 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">掉寶率提高。</t>
+          <t xml:space="preserve">反震傷害提高。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">penUp</t>
+          <t xml:space="preserve">lootUp</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理/魔法穿透</t>
+          <t xml:space="preserve">掉寶</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">🗡️</t>
+          <t xml:space="preserve">🎁</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1241,7 +1246,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">penUp</t>
+          <t xml:space="preserve">lootUp</t>
         </is>
       </c>
       <c r="I20">
@@ -1251,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -1269,24 +1274,24 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法穿透提高。</t>
+          <t xml:space="preserve">掉寶率提高。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">allDmgUp</t>
+          <t xml:space="preserve">penUp</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">時空凝滯·所有傷害</t>
+          <t xml:space="preserve">物理/魔法穿透</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌌</t>
+          <t xml:space="preserve">🗡️</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1301,7 +1306,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">allDmgUp</t>
+          <t xml:space="preserve">penUp</t>
         </is>
       </c>
       <c r="I21">
@@ -1311,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M21">
         <v>5</v>
@@ -1329,24 +1334,24 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潛力【時空凝滯】：所有傷害提高。</t>
+          <t xml:space="preserve">物理與魔法穿透提高。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">velocitySurge</t>
+          <t xml:space="preserve">allDmgUp</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">極速之力·攻速</t>
+          <t xml:space="preserve">時空凝滯·所有傷害</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">💨</t>
+          <t xml:space="preserve">🌌</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1361,7 +1366,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">velocitySurge</t>
+          <t xml:space="preserve">allDmgUp</t>
         </is>
       </c>
       <c r="I22">
@@ -1389,24 +1394,24 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t xml:space="preserve">潛力【極速之力】：攻速提高。</t>
+          <t xml:space="preserve">潛力【時空凝滯】：所有傷害提高。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightningOverload</t>
+          <t xml:space="preserve">velocitySurge</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷霆過載·雷電傷害</t>
+          <t xml:space="preserve">極速之力·攻速</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">💨</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1421,12 +1426,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightningOverload</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">velocitySurge</t>
         </is>
       </c>
       <c r="I23">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潛力【雷霆過載】：雷電傷害提高。</t>
+          <t xml:space="preserve">潛力【極速之力】：攻速提高。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">chronoCdr</t>
+          <t xml:space="preserve">lightningOverload</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">時間坍縮·冷卻縮減</t>
+          <t xml:space="preserve">雷霆過載·雷電傷害</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">⏱️</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1486,7 +1486,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">chronoCdr</t>
+          <t xml:space="preserve">lightningOverload</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="I24">
@@ -1514,24 +1519,24 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t xml:space="preserve">潛力【時間坍縮】：冷卻縮減。</t>
+          <t xml:space="preserve">潛力【雷霆過載】：雷電傷害提高。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacredInvert</t>
+          <t xml:space="preserve">chronoCdr</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖療逆轉·回復/溢傷</t>
+          <t xml:space="preserve">時間坍縮·冷卻縮減</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">🕊️</t>
+          <t xml:space="preserve">⏱️</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1546,12 +1551,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacredInvert</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">light</t>
+          <t xml:space="preserve">chronoCdr</t>
         </is>
       </c>
       <c r="I25">
@@ -1579,24 +1579,24 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t xml:space="preserve">潛力【聖療逆轉】：回復與溢傷轉換。</t>
+          <t xml:space="preserve">潛力【時間坍縮】：冷卻縮減。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">legendaryDarkUp</t>
+          <t xml:space="preserve">sacredInvert</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">暗影強化</t>
+          <t xml:space="preserve">聖療逆轉·回復/溢傷</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌑</t>
+          <t xml:space="preserve">🕊️</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">legendaryDarkUp</t>
+          <t xml:space="preserve">sacredInvert</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">dark</t>
+          <t xml:space="preserve">light</t>
         </is>
       </c>
       <c r="I26">
@@ -1644,24 +1644,24 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t xml:space="preserve">傳奇特效：暗屬性傷害提高。</t>
+          <t xml:space="preserve">潛力【聖療逆轉】：回復與溢傷轉換。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">legendaryGuardRed</t>
+          <t xml:space="preserve">legendaryDarkUp</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">守護減傷</t>
+          <t xml:space="preserve">暗影強化</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">🛡️</t>
+          <t xml:space="preserve">🌑</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1676,7 +1676,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">legendaryGuardRed</t>
+          <t xml:space="preserve">legendaryDarkUp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dark</t>
         </is>
       </c>
       <c r="I27">
@@ -1704,24 +1709,24 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">傳奇特效：受到的傷害降低。</t>
+          <t xml:space="preserve">傳奇特效：暗屬性傷害提高。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">legendaryLightShieldRed</t>
+          <t xml:space="preserve">legendaryGuardRed</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖盾減傷</t>
+          <t xml:space="preserve">守護減傷</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔆</t>
+          <t xml:space="preserve">🛡️</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1736,12 +1741,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">legendaryLightShieldRed</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">light</t>
+          <t xml:space="preserve">legendaryGuardRed</t>
         </is>
       </c>
       <c r="I28">
@@ -1776,22 +1776,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">atkDown</t>
+          <t xml:space="preserve">legendaryLightShieldRed</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊</t>
+          <t xml:space="preserve">聖盾減傷</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚔️</t>
+          <t xml:space="preserve">🔆</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">debuff</t>
+          <t xml:space="preserve">buff</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1801,7 +1801,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">atkDown</t>
+          <t xml:space="preserve">legendaryLightShieldRed</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">light</t>
         </is>
       </c>
       <c r="I29">
@@ -1811,10 +1816,10 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -1829,24 +1834,24 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t xml:space="preserve">目標攻擊力下降。</t>
+          <t xml:space="preserve">傳奇特效：受到的傷害降低。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">defDown</t>
+          <t xml:space="preserve">atkDown</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">防禦</t>
+          <t xml:space="preserve">攻擊</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">🛡️</t>
+          <t xml:space="preserve">⚔️</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1861,7 +1866,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">defDown</t>
+          <t xml:space="preserve">atkDown</t>
         </is>
       </c>
       <c r="I30">
@@ -1871,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M30">
         <v>6</v>
@@ -1889,65 +1894,125 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve">目標防禦力下降（舊存檔融合技快照相容保留，新設計改用穿透提升）。</t>
+          <t xml:space="preserve">目標攻擊力下降。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t xml:space="preserve">defDown</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">防禦</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🛡️</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">defDown</t>
+        </is>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>6</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P31">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">目標防禦力下降（舊存檔融合技快照相容保留，新設計改用穿透提升）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t xml:space="preserve">enemyAspdDown</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t xml:space="preserve">時間結界·攻速</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t xml:space="preserve">⏳</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t xml:space="preserve">debuff</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t xml:space="preserve">stat</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t xml:space="preserve">enemyAspdDown</t>
         </is>
       </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
         <v>5</v>
       </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t xml:space="preserve">refresh</t>
         </is>
       </c>
-      <c r="P31">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="inlineStr">
+      <c r="P32">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t xml:space="preserve">潛力【時間結界】：目標攻擊速度下降。</t>
         </is>
@@ -2054,277 +2119,326 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">效果鍵值</t>
-        </is>
-      </c>
-    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shield＝吸收護盾（占施法者最大生命%，吃護盾效率；被打完或時間到就消失）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態效果＝stat 時填增益鍵：atkUp/defUp/aspdUp/evasionUp/critDmgUp/blockUp/thornsUp/lootUp/penUp/atkDown/defDown/enemyAspdDown 等；</t>
+          <t xml:space="preserve">效果鍵值</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態效果＝ctrl 時填 stun（暈眩）/slow（減速）/invuln（無敵）；</t>
+          <t xml:space="preserve">狀態效果＝stat 時填增益鍵：atkUp/defUp/aspdUp/evasionUp/critDmgUp/blockUp/thornsUp/lootUp/penUp/atkDown/defDown/enemyAspdDown 等；</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態效果＝hot 時固定填 hot；dot 留空；</t>
+          <t xml:space="preserve">狀態效果＝ctrl 時填 stun（暈眩）/slow（減速）/invuln（無敵）；</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t xml:space="preserve">狀態效果＝hot 時固定填 hot；shield 時固定填 shield；dot 留空；</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t xml:space="preserve">注意：這是接線鍵，對應戰鬥程式讀取的欄位，不要自行改名；</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">傷害屬性</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">fire＝火／ice＝冰／lightning＝雷／poison＝毒／light＝聖／dark＝暗；空白＝無屬性；</t>
+          <t xml:space="preserve">傷害屬性</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t xml:space="preserve">fire＝火／ice＝冰／lightning＝雷／poison＝毒／light＝聖／dark＝暗；空白＝無屬性；</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t xml:space="preserve">用途：持續傷害的屬性歸屬（顯示與分類用）；</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">傷害來源</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">skill＝占「施放當下的技能傷害」百分比（燃燒、流血、中毒…）；</t>
+          <t xml:space="preserve">傷害來源</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">maxHp＝占「目標最大生命」百分比（死亡詛咒）；</t>
+          <t xml:space="preserve">skill＝占「施放當下的技能傷害」百分比（燃燒、流血、中毒…）；</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t xml:space="preserve">maxHp＝占「目標最大生命」百分比（死亡詛咒）；持續回復與護盾則是占「施法者最大生命」百分比；</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t xml:space="preserve">value＝直接數值（不經百分比換算）；</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">狀態傷害</t>
-        </is>
-      </c>
-    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">每次作用的量，依「傷害來源」解讀（skill/maxHp 填百分比數字，value 填數值）；</t>
+          <t xml:space="preserve">狀態傷害</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態效果＝hot 時＝每秒回復的最大生命%；stat／ctrl 不使用本欄；</t>
+          <t xml:space="preserve">每次作用的量，依「傷害來源」解讀（skill/maxHp 填百分比數字，value 填數值）；</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t xml:space="preserve">狀態效果＝hot 時＝每秒回復的最大生命%；shield 時＝護盾量占最大生命%；stat／ctrl 不使用本欄；</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t xml:space="preserve">技能可在自己的 fx 覆寫本欄（例：火球術的燃燒 20%、隕石術的燃燒 30%）；</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">傷害上限參照 / 傷害上限倍率</t>
-        </is>
-      </c>
-    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">上限＝施法者的該項屬性 × 倍率（例：matk 與 6 ＝ 魔攻 ×6）；參照欄留空＝無上限；</t>
+          <t xml:space="preserve">傷害上限參照 / 傷害上限倍率</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t xml:space="preserve">上限＝施法者的該項屬性 × 倍率（例：matk 與 6 ＝ 魔攻 ×6）；參照欄留空＝無上限；</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t xml:space="preserve">用途：避免「占最大生命%」型的持續傷害在高血量敵人身上暴衝；</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">效果數值</t>
-        </is>
-      </c>
-    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態效果＝stat 時的增減幅度%（例：攻擊提升 15 ＝ 攻擊力 +15%）；dot／hot／ctrl 不使用；</t>
+          <t xml:space="preserve">效果數值</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t xml:space="preserve">狀態效果＝stat 時的增減幅度%（例：攻擊提升 15 ＝ 攻擊力 +15%）；dot／hot／ctrl 不使用；</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t xml:space="preserve">技能可在自己的 fx 覆寫本欄；</t>
         </is>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">持續時間</t>
-        </is>
-      </c>
-    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態生效的秒數；技能可在自己的 fx 覆寫（保留里程碑成長）；</t>
+          <t xml:space="preserve">持續時間</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">注意：控場類（暈眩、減速）的實際秒數還會再乘上控場遞減與目標韌性；</t>
-        </is>
-      </c>
-    </row>
-    <row r="49"/>
+          <t xml:space="preserve">狀態生效的秒數；技能可在自己的 fx 覆寫（保留里程碑成長）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">護盾（shield）也吃這一欄：時間到時還沒被打掉的護盾會一併消失；</t>
+        </is>
+      </c>
+    </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">作用間隔時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">持續傷害每隔幾秒結算一次（例：1 ＝ 每秒跳一次傷害）；</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">注意：控場類（暈眩、減速）的實際秒數還會再乘上控場遞減與目標韌性；</t>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">0＝不分段，改為連續結算（每一幀依比例扣血）；stat／ctrl 類填 0；</t>
+          <t xml:space="preserve">作用間隔時間</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">注意：狀態到期時會把不足一次間隔的餘額補跳，所以「總傷害＝狀態傷害×(持續時間÷作用間隔)」恆成立，</t>
+          <t xml:space="preserve">持續傷害每隔幾秒結算一次（例：1 ＝ 每秒跳一次傷害）；</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　調整作用間隔只改變跳傷的節奏，不改變總量；</t>
-        </is>
-      </c>
-    </row>
-    <row r="55"/>
+          <t xml:space="preserve">0＝不分段，改為連續結算（每一幀依比例扣血）；stat／ctrl 類填 0；</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注意：狀態到期時會把不足一次間隔的餘額補跳，所以「總傷害＝狀態傷害×(持續時間÷作用間隔)」恆成立，</t>
+        </is>
+      </c>
+    </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">疊加規則 / 最大疊層</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">refresh＝重新計時（後蓋前）；strongest＝取高並重新計時（目前持續傷害採用）；stack＝疊層；</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">　　　調整作用間隔只改變跳傷的節奏，不改變總量；</t>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">最大疊層＝疊加規則為 stack 時的上限，其餘填 1；</t>
-        </is>
-      </c>
-    </row>
-    <row r="59"/>
+          <t xml:space="preserve">疊加規則 / 最大疊層</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh＝重新計時（後蓋前，增益的預設）；</t>
+        </is>
+      </c>
+    </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">── 新增狀態注意 ──</t>
+          <t xml:space="preserve">strongest＝取高並重新計時（目前持續傷害採用）；</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. 新增一列即可新增狀態；要讓技能用到它，還要在 Skills 表該技能的「基礎fx(JSON)」加 status 引用，</t>
+          <t xml:space="preserve">stack＝疊層：重複施加時「單層值取高、層數 +1」直到最大疊層，實際效果值＝單層值 × 層數；</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   例：{"dmgType":"magic","stat":"matk","base":300,"per":60,"status":[{"id":"burn"}]}；</t>
+          <t xml:space="preserve">　　　　持續時間一律以最後一次施加重新計時，層數不會各自倒數；</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. status 陣列可帶 dmg／dur／val 覆寫本表預設值，例 {"id":"burn","dmg":35,"dur":5}；不帶就吃本表的值；</t>
+          <t xml:space="preserve">最大疊層＝疊加規則為 stack 時的上限（必須大於 1），其餘規則填 1；</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">把任何一列的疊加規則改成 stack、最大疊層填 2 以上，該狀態立刻就會疊層，不必改程式；</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">戰鬥畫面與提示框會在狀態名後面顯示「×層數」；</t>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">── 新增狀態注意 ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 新增一列即可新增狀態；要讓技能用到它，還要在 Skills 表該技能的「基礎fx(JSON)」加 status 引用，</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   例：{"dmgType":"magic","stat":"matk","base":300,"per":60,"status":[{"id":"burn"}]}；</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. status 陣列可帶 dmg／dur／val 覆寫本表預設值，例 {"id":"burn","dmg":35,"dur":5}；不帶就吃本表的值；</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t xml:space="preserve">3. 狀態效果＝stat／ctrl 的「效果鍵值」必須是程式認得的鍵，不能自創；dot／hot 則可自由新增。</t>
         </is>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -2018,6 +2018,431 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgBleed</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">血刃流血</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🩸</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dot</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skill</t>
+        </is>
+      </c>
+      <c r="I33">
+        <v>30</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>5</v>
+      </c>
+      <c r="N33">
+        <v>1</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strongest</t>
+        </is>
+      </c>
+      <c r="P33">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【血刃斬】：每次作用造成技能傷害一定比例的傷害；每跳量與間隔由技能各階決定（引擎以 dps 覆寫）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgPoison</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">血刃劇毒</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">☠️</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poison</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skill</t>
+        </is>
+      </c>
+      <c r="I34">
+        <v>25</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>4</v>
+      </c>
+      <c r="N34">
+        <v>0.5</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strongest</t>
+        </is>
+      </c>
+      <c r="P34">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【血毒刃】：毒屬性持續傷害；每跳量與間隔由技能各階決定（引擎以 dps 覆寫）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgIronBleed</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鐵血裂傷</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🗡️</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dot</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maxHp</t>
+        </is>
+      </c>
+      <c r="I35">
+        <v>3.5</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>3</v>
+      </c>
+      <c r="N35">
+        <v>0.35</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P35">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【鐵血之舞】：占最大生命比例的流血；自身流血直接扣生命、不吃護盾。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgGale</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狂風</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">💨</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgGale</t>
+        </is>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>20</v>
+      </c>
+      <c r="M36">
+        <v>5</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P36">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【狂風斬】：攻速額外提高（突破攻速上限、與自身攻速相乘）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgFrenzyCr</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狂暴·爆擊率</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔥</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgCritUp</t>
+        </is>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>50</v>
+      </c>
+      <c r="M37">
+        <v>6</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P37">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【狂暴之舞】：爆擊率提高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgFrenzyCd</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狂暴·爆擊傷害</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">💥</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgCritDmgUp</t>
+        </is>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>200</v>
+      </c>
+      <c r="M38">
+        <v>6</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P38">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【狂暴之舞】：爆擊傷害提高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgStorm</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風化身</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgStorm</t>
+        </is>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>3</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P39">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【暴風之舞】：化身暴風，期間自動施放雙刀亂舞、無法普攻。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -2443,6 +2443,126 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgBloodrage</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">嗜血狂怒</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">💢</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgBloodrage</t>
+        </is>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>20</v>
+      </c>
+      <c r="M40">
+        <v>8</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P40">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【嗜血狂怒】：攻速乘算提高（突破攻速上限）；期間各階狂怒效果生效。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgArmorBrk</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">破甲</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚒️</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgDefBrk</t>
+        </is>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>25</v>
+      </c>
+      <c r="M41">
+        <v>4</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stack</t>
+        </is>
+      </c>
+      <c r="P41">
+        <v>4</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【破甲擊】：防禦降低（可疊層，疊層時重置時間；獨立鍵、與舊 defDown 減益加總計算）。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -2563,6 +2563,136 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgBurn</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">烈焰燃燒</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔥</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skill</t>
+        </is>
+      </c>
+      <c r="I42">
+        <v>20</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>5</v>
+      </c>
+      <c r="N42">
+        <v>0.5</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strongest</t>
+        </is>
+      </c>
+      <c r="P42">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【火球術／火柱】：火屬性持續傷害；每跳量與間隔由技能各階決定（引擎以 dps 覆寫）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgFireAmp</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火焰增幅</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔥</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgFireAmp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>4</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P43">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【火焰增幅】：火屬性傷害提升（層數由引擎累加成單一數值，故用後蓋前並重置時間）。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -2693,6 +2693,71 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgFirehunt</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgFirehunt</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>4</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P44">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【火狩】：火狩環繞自身的剩餘時間；【再生】的擊殺延長會累加在這裡。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -2758,6 +2758,326 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgRockArmor</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">岩甲</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🪨</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgRockArmor</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>10</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P45">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【岩甲術】：岩甲護盾的剩餘時間；第 3、5、6、7 階的效果只在此期間生效（護盾本身走「護盾」狀態）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgRockAmp</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">岩甲增幅</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🪨</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgRockAmp</t>
+        </is>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>3</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P46">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【岩甲增幅】：損失護盾換得的傷害增幅（層數由引擎累加成單一數值，故用後蓋前並重置時間）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgMire</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">泥沼緩速</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgMire</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>50</v>
+      </c>
+      <c r="M47">
+        <v>1</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P47">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【泥沼術】：攻速與移動速度下降（效果值＝攻速下降%）。同類型緩速依「取代」規則後蓋前並重新計時；為場域型持續重塗，不吃控場遞減與韌性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgMirePoison</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">泥沼劇毒</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">☠️</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poison</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skill</t>
+        </is>
+      </c>
+      <c r="I48">
+        <v>25</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>1</v>
+      </c>
+      <c r="N48">
+        <v>0.5</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P48">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【毒沼術】：毒性持續傷害；每跳量與間隔由技能各階決定（引擎以 dps 覆寫），站在沼澤中才會被重塗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgMireLava</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">熔岩灼燒</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌋</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skill</t>
+        </is>
+      </c>
+      <c r="I49">
+        <v>70</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>1</v>
+      </c>
+      <c r="N49">
+        <v>0.4</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P49">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【熔岩沼】：火焰持續傷害；每跳量與間隔由技能各階決定（引擎以 dps 覆寫），站在岩漿中才會被重塗。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -3078,6 +3078,71 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgThunderOrb</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環體電球</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgThunderOrb</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>6</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P50">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【環體電球】：電球環繞自身的剩餘時間（與火狩各自一格，兩者互不覆蓋）。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -3143,6 +3143,266 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgFrost</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寒霜</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">❄️</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgFrost</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>20</v>
+      </c>
+      <c r="M51">
+        <v>5</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stack</t>
+        </is>
+      </c>
+      <c r="P51">
+        <v>5</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【寒霜狀態】的層數與緩速：每疊 1 層使移動與攻擊速度各下降（效果值＝單層下降% × 層數），疊滿層數時凍結。比照泥沼緩速為場域型重塗，緩速本身不吃控場遞減與韌性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgFrostBite</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寒霜凍傷</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🧊</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skill</t>
+        </is>
+      </c>
+      <c r="I52">
+        <v>50</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>5</v>
+      </c>
+      <c r="N52">
+        <v>0.5</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strongest</t>
+        </is>
+      </c>
+      <c r="P52">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【寒霜狀態】的寒冰持續傷害；每跳量占施放群組的本體技能傷害（引擎以 dps 覆寫）。依使用者決策，傷害不隨寒霜層數提高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgFrozen</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">凍結</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🥶</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgFrozen</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>3</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P53">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【寒霜狀態】疊滿層數的凍結標記。行動限制本身由「暈眩」承擔（因此完整沿用 BOSS 控場免疫、韌性折減與控場遞減），本狀態只標記「正在凍結中」，供【水龍捲】增傷與【寒冰爆裂箭】判定冰爆時機。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgIceRevert</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寒冰逆轉</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">💧</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgIceRevert</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>20</v>
+      </c>
+      <c r="M54">
+        <v>6</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P54">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【寒冰逆轉】：敵人的屬性標籤強制改為寒冰，且受到的寒冰傷害提高（效果值＝提高%）。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -3403,6 +3403,396 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgWindRend</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風切</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌀</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgWindRend</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>80</v>
+      </c>
+      <c r="M55">
+        <v>4</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stack</t>
+        </is>
+      </c>
+      <c r="P55">
+        <v>3</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【風切狀態】的層數與減益：移動速度下降（效果值＝下降%）、命中率下降，層數上限由【無限風切】開放。比照泥沼緩速為技能型減益，不吃控場遞減與韌性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgWindCut</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風切割裂</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">💨</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skill</t>
+        </is>
+      </c>
+      <c r="I56">
+        <v>50</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>4</v>
+      </c>
+      <c r="N56">
+        <v>0.5</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strongest</t>
+        </is>
+      </c>
+      <c r="P56">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【風切狀態】的風系持續傷害；每跳量占施放群組的本體技能傷害並隨風切層數提高（引擎以 dps 覆寫）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgWindSlow</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狂風緩速</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgWindSlow</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>60</v>
+      </c>
+      <c r="M57">
+        <v>3</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P57">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【狂風碎裂】：被風刃命中的敵人移動速度下降（效果值＝下降%）。同類型緩速依「取代」規則後蓋前並重新計時。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgStormBarrier</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgStormBarrier</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>10</v>
+      </c>
+      <c r="M58">
+        <v>8</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P58">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【暴風屏障】：屏障的剩餘時間與傷害減免（效果值＝減免%）；第 2～6 階的效果只在此期間生效（護盾由節拍逐次給予）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgVoidBlade</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">虛空斬</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌀</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgVoidBlade</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>6</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P59">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【虛空斬】：虛空斬擊還會在場上繞行多久（環繞場域的剩餘時間投影，比照火狩）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgStormGod</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風神體</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⛈️</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgStormGod</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>99</v>
+      </c>
+      <c r="M60">
+        <v>2</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P60">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版技能【暴風神體】：風暴之神附體期間的傷害減免（效果值＝減免%），且風系傷害額外乘算提高。與暴風屏障是分開的兩個狀態。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -3471,12 +3471,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">sgWindCut</t>
+          <t xml:space="preserve">sgWindRend</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切割裂</t>
+          <t xml:space="preserve">風切</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3491,7 +3491,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">dot</t>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgWindRend</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3499,54 +3504,49 @@
           <t xml:space="preserve">wind</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">skill</t>
-        </is>
-      </c>
       <c r="I56">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M56">
         <v>4</v>
       </c>
       <c r="N56">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t xml:space="preserve">strongest</t>
+          <t xml:space="preserve">stack</t>
         </is>
       </c>
       <c r="P56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t xml:space="preserve">新版技能【風切狀態】的風系持續傷害；每跳量占施放群組的本體技能傷害並隨風切層數提高（引擎以 dps 覆寫）。</t>
+          <t xml:space="preserve">新版技能【風切狀態】的減益本體：移動速度下降（效果值＝單層下降%，不隨層數再加深）且命中率下降；層數只影響風切割裂的每跳傷害，當下允許的層數上限由真空斬【無限風切】決定。</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">sgWindSlow</t>
+          <t xml:space="preserve">sgWindCut</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂風緩速</t>
+          <t xml:space="preserve">風切割裂</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
+          <t xml:space="preserve">💨</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3556,12 +3556,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">stat</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sgWindSlow</t>
+          <t xml:space="preserve">dot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3569,24 +3564,29 @@
           <t xml:space="preserve">wind</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skill</t>
+        </is>
+      </c>
       <c r="I57">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K57">
         <v>0</v>
       </c>
       <c r="L57">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t xml:space="preserve">refresh</t>
+          <t xml:space="preserve">strongest</t>
         </is>
       </c>
       <c r="P57">
@@ -3594,29 +3594,29 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t xml:space="preserve">新版技能【狂風碎裂】：被風刃命中的敵人移動速度下降（效果值＝下降%）。同類型緩速依「取代」規則後蓋前並重新計時。</t>
+          <t xml:space="preserve">新版技能【風切狀態】的風系持續傷害；每跳量占施放群組的本體技能傷害並隨風切層數提高（引擎以 dps 覆寫）。</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">sgStormBarrier</t>
+          <t xml:space="preserve">sgWindSlow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">狂風緩速</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🍃</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">buff</t>
+          <t xml:space="preserve">debuff</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">sgStormBarrier</t>
+          <t xml:space="preserve">sgWindSlow</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3641,10 +3641,10 @@
         <v>0</v>
       </c>
       <c r="L58">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="M58">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N58">
         <v>0</v>
@@ -3659,24 +3659,24 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t xml:space="preserve">新版技能【暴風屏障】：屏障的剩餘時間與傷害減免（效果值＝減免%）；第 2～6 階的效果只在此期間生效（護盾由節拍逐次給予）。</t>
+          <t xml:space="preserve">新版技能【狂風碎裂】：被風刃命中的敵人移動速度下降（效果值＝下降%）。同類型緩速依「取代」規則後蓋前並重新計時。</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">sgVoidBlade</t>
+          <t xml:space="preserve">sgStormBarrier</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">虛空斬</t>
+          <t xml:space="preserve">暴風屏障</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🌪️</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">sgVoidBlade</t>
+          <t xml:space="preserve">sgStormBarrier</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3706,10 +3706,10 @@
         <v>0</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M59">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N59">
         <v>0</v>
@@ -3724,24 +3724,24 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t xml:space="preserve">新版技能【虛空斬】：虛空斬擊還會在場上繞行多久（環繞場域的剩餘時間投影，比照火狩）。</t>
+          <t xml:space="preserve">新版技能【暴風屏障】：屏障的剩餘時間與傷害減免（效果值＝減免%）；第 2～6 階的效果只在此期間生效（護盾由節拍逐次給予）。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">sgStormGod</t>
+          <t xml:space="preserve">sgVoidBlade</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風神體</t>
+          <t xml:space="preserve">虛空斬</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">⛈️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">sgStormGod</t>
+          <t xml:space="preserve">sgVoidBlade</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="M60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N60">
         <v>0</v>
@@ -3789,29 +3789,29 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t xml:space="preserve">新版技能【暴風神體】：風暴之神附體期間的傷害減免（效果值＝減免%），且風系傷害額外乘算提高。與暴風屏障是分開的兩個狀態。</t>
+          <t xml:space="preserve">新版技能【虛空斬】：虛空斬擊還會在場上繞行多久（環繞場域的剩餘時間投影，比照火狩）。</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">sgThrustVuln</t>
+          <t xml:space="preserve">sgStormGod</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">千瘡百孔</t>
+          <t xml:space="preserve">暴風神體</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">🕳️</t>
+          <t xml:space="preserve">⛈️</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">debuff</t>
+          <t xml:space="preserve">buff</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3821,7 +3821,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">sgThrustVuln</t>
+          <t xml:space="preserve">sgStormGod</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
         </is>
       </c>
       <c r="I61">
@@ -3831,42 +3836,42 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="M61">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N61">
         <v>0</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t xml:space="preserve">stack</t>
+          <t xml:space="preserve">refresh</t>
         </is>
       </c>
       <c r="P61">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t xml:space="preserve">傳奇特效【千瘡百孔】：每次突刺命中疊 1 層，每層使該敵人受到的傷害提高（效果值＝單層提高%）；層數上限由特效參數決定。</t>
+          <t xml:space="preserve">新版技能【暴風神體】：風暴之神附體期間的傷害減免（效果值＝減免%），且風系傷害額外乘算提高。與暴風屏障是分開的兩個狀態。</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">sgSoulRend</t>
+          <t xml:space="preserve">sgThrustVuln</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">靈魂撕裂</t>
+          <t xml:space="preserve">千瘡百孔</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">👻</t>
+          <t xml:space="preserve">🕳️</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3881,12 +3886,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">sgSoulRend</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dark</t>
+          <t xml:space="preserve">sgThrustVuln</t>
         </is>
       </c>
       <c r="I62">
@@ -3896,10 +3896,10 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M62">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="N62">
         <v>0</v>
@@ -3910,28 +3910,28 @@
         </is>
       </c>
       <c r="P62">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t xml:space="preserve">超神進化【暗影絕殺者】：每次突刺命中疊 1 層，每層使該敵人受到的傷害提高（效果值＝單層提高%）；層數上限與單層值由技能參數決定。</t>
+          <t xml:space="preserve">傳奇特效【千瘡百孔】：每次突刺命中疊 1 層，每層使該敵人受到的傷害提高（效果值＝單層提高%）；層數上限由特效參數決定。</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">sgThrustBleed</t>
+          <t xml:space="preserve">sgSoulRend</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">穿心裂血</t>
+          <t xml:space="preserve">靈魂撕裂</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">🩸</t>
+          <t xml:space="preserve">👻</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3941,100 +3941,285 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">dot</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">skill</t>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgSoulRend</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dark</t>
         </is>
       </c>
       <c r="I63">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="N63">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t xml:space="preserve">strongest</t>
+          <t xml:space="preserve">stack</t>
         </is>
       </c>
       <c r="P63">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t xml:space="preserve">傳奇特效【穿心裂血】：突刺附加的流血；每跳量與間隔由特效參數決定（引擎以 dps 覆寫）。</t>
+          <t xml:space="preserve">超神進化【暗影絕殺者】：每次突刺命中疊 1 層，每層使該敵人受到的傷害提高（效果值＝單層提高%）；層數上限與單層值由技能參數決定。</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t xml:space="preserve">sgThrustBleed</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">穿心裂血</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🩸</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dot</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skill</t>
+        </is>
+      </c>
+      <c r="I64">
+        <v>50</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>5</v>
+      </c>
+      <c r="N64">
+        <v>0.5</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strongest</t>
+        </is>
+      </c>
+      <c r="P64">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傳奇特效【穿心裂血】：突刺附加的流血；每跳量與間隔由特效參數決定（引擎以 dps 覆寫）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t xml:space="preserve">sgPhantomDodge</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t xml:space="preserve">幻影殘像</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t xml:space="preserve">🌫️</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t xml:space="preserve">buff</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t xml:space="preserve">stat</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t xml:space="preserve">sgPhantomDodge</t>
         </is>
       </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
-      </c>
-      <c r="L64">
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
         <v>30</v>
       </c>
-      <c r="M64">
+      <c r="M65">
         <v>2</v>
       </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64" t="inlineStr">
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65" t="inlineStr">
         <is>
           <t xml:space="preserve">refresh</t>
         </is>
       </c>
-      <c r="P64">
-        <v>1</v>
-      </c>
-      <c r="Q64" t="inlineStr">
+      <c r="P65">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【幻影八方陣】：期間有一定機率絕對閃避敵方攻擊（效果值＝機率%）；此擲骰與命中率無關，先於命中判定結算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgDeathReaper</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">死亡收割</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">☠️</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgDeathReaper</t>
+        </is>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>25</v>
+      </c>
+      <c r="M66">
+        <v>8</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stack</t>
+        </is>
+      </c>
+      <c r="P66">
+        <v>20</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超神進化【死亡收割者】：飛刀每殺死 1 個敵人疊 1 層，每層使你造成的所有傷害提高（效果值＝單層提高%）；層數上限與單層值由技能參數決定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgKnifeWaltz</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">輪舞刃</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔪</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgKnifeWaltz</t>
+        </is>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>5</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P67">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傳奇特效【輪舞刃】：繞行在你周圍的飛刀還會留在場上多久（環繞場域的剩餘時間投影，比照火狩）。</t>
         </is>
       </c>
     </row>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -4223,6 +4223,316 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgSlayerMark</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">殺神</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚰️</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgSlayerMark</t>
+        </is>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>2</v>
+      </c>
+      <c r="M68">
+        <v>6</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stack</t>
+        </is>
+      </c>
+      <c r="P68">
+        <v>100</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超神進化【殺神領域】：領域內的敵人死亡時疊 1 層，每層使你造成的所有傷害提高（效果值＝單層% × 層數）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgVenomField</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">萬毒侵蝕</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🧪</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poison</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skill</t>
+        </is>
+      </c>
+      <c r="I69">
+        <v>100</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>6</v>
+      </c>
+      <c r="N69">
+        <v>0.5</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stack</t>
+        </is>
+      </c>
+      <c r="P69">
+        <v>10</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超神進化【萬毒血霧】：領域內每次作用疊 1 層，每跳量＝單層量 × 層數（引擎以 dps 覆寫）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgKagura</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神樂灼焰</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🎇</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skill</t>
+        </is>
+      </c>
+      <c r="I70">
+        <v>10</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>6</v>
+      </c>
+      <c r="N70">
+        <v>0.5</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stack</t>
+        </is>
+      </c>
+      <c r="P70">
+        <v>20</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超神進化【火之神樂】：雙刀亂舞每命中 1 次疊 1 層，每跳量＝單層量 × 層數（引擎以 dps 覆寫）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgDeathDefer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不屈之誓</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🕯️</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgDeathDefer</t>
+        </is>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>100</v>
+      </c>
+      <c r="M71">
+        <v>10</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P71">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傳奇【不屈之誓】：死亡延後生效的期間，你造成的所有傷害提高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgBloodMist</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">血霧壟罩</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌫️</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgBloodMist</t>
+        </is>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0.6</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P72">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傳奇【血霧】：站在血霧裡的標記，受傷時回復施放者生命。效果值為 0＝本身不改變任何屬性。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t xml:space="preserve">傳奇【血霧】：站在血霧裡的標記，受傷時回復施放者生命。效果值為 0＝本身不改變任何屬性。</t>
+          <t xml:space="preserve">傳奇【血霧】：站在血霧裡的標記，受傷時回復施放者生命。效果值＝血霧生成當下定版的回復比例%（沒有任何屬性讀這個鍵，它只是把數值帶在標記上）。</t>
         </is>
       </c>
     </row>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -4533,6 +4533,306 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgCounterWrath</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">怒火</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">😡</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgCounterWrath</t>
+        </is>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>30</v>
+      </c>
+      <c r="M73">
+        <v>6</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P73">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傳奇【怒火】：反擊累積達門檻時獲得，期間你造成的所有傷害提高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgBurnBlood</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">燃血</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🩸</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgBurnBlood</t>
+        </is>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>1</v>
+      </c>
+      <c r="M74">
+        <v>4</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stack</t>
+        </is>
+      </c>
+      <c r="P74">
+        <v>50</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傳奇【燃血】：【血飲術】每造成 1 次自身生命損失疊 1 層，每層使你造成的所有傷害提高（效果值＝單層% × 層數）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgThornsRage</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">屠戮</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🪓</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgThornsRage</t>
+        </is>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>5</v>
+      </c>
+      <c r="M75">
+        <v>4</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stack</t>
+        </is>
+      </c>
+      <c r="P75">
+        <v>10</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傳奇【屠戮者】：狂怒期間每擊殺 1 個敵人疊 1 層，每層使【嗜血反震】的效果提高（效果值＝單層% × 層數）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgWarGodKill</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">戰神屠錄</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📜</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgWarGodKill</t>
+        </is>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>4</v>
+      </c>
+      <c r="M76">
+        <v>99999</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stack</t>
+        </is>
+      </c>
+      <c r="P76">
+        <v>100</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超神進化【戰神屠錄】：狂怒期間每擊殺 1 個敵人疊 1 層，每層使你造成的所有傷害提高（效果值＝單層% × 層數）；設計為「持續到死亡為止」，因此持續時間給一個單場戰鬥不可能走完的值，實際回收靠死亡時的 resetSkill2RT。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgAsuraFist</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阿修羅霸王拳</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">👊</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgAsuraFist</t>
+        </is>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>500</v>
+      </c>
+      <c r="M77">
+        <v>1</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P77">
+        <v>1</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超神進化【阿修羅霸王拳】：每隔一段時間自動發動，短暫期間內你造成的所有傷害大幅提高。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -4833,6 +4833,71 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgBurnAmp</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">爆燃</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔥</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgBurnAmp</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>10</v>
+      </c>
+      <c r="M78">
+        <v>4</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P78">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傳奇特效【爆燃】：火龍捲每造成 1 段傷害就疊 1 層，使該敵人受到的燃燒傷害提高（效果值＝目前的總提高%）。設計文檔未設層數上限，因此比照【火焰增幅】由引擎累加成單一數值後「後蓋前」，不使用狀態表的疊層規則。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -4836,63 +4836,128 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t xml:space="preserve">sgStarfall</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地爆天星</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgStarfall</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>60</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P78">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超神進化【地爆天星】：距離下一顆超巨型殞石落下還有多久（剩餘時間即倒數，效果值本身沒有意義；比照【暴風化身】【火狩】的純計時狀態）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t xml:space="preserve">sgBurnAmp</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t xml:space="preserve">爆燃</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t xml:space="preserve">🔥</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t xml:space="preserve">debuff</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stat</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t xml:space="preserve">sgBurnAmp</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">fire</t>
         </is>
       </c>
-      <c r="I78">
-        <v>0</v>
-      </c>
-      <c r="K78">
-        <v>0</v>
-      </c>
-      <c r="L78">
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
         <v>10</v>
       </c>
-      <c r="M78">
+      <c r="M79">
         <v>4</v>
       </c>
-      <c r="N78">
-        <v>0</v>
-      </c>
-      <c r="O78" t="inlineStr">
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79" t="inlineStr">
         <is>
           <t xml:space="preserve">refresh</t>
         </is>
       </c>
-      <c r="P78">
-        <v>1</v>
-      </c>
-      <c r="Q78" t="inlineStr">
+      <c r="P79">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="inlineStr">
         <is>
           <t xml:space="preserve">傳奇特效【爆燃】：火龍捲每造成 1 段傷害就疊 1 層，使該敵人受到的燃燒傷害提高（效果值＝目前的總提高%）。設計文檔未設層數上限，因此比照【火焰增幅】由引擎累加成單一數值後「後蓋前」，不使用狀態表的疊層規則。</t>
         </is>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -4963,6 +4963,136 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgPetrify</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">石化</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🗿</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgPetrify</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>400</v>
+      </c>
+      <c r="M80">
+        <v>4</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P80">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超神進化【超重岩之術】：被壓縮的巨岩之力封住的敵人。行動限制本身由「暈眩」承擔（因此完整沿用 BOSS 控場免疫、韌性折減與控場遞減），本狀態只負責「受到的土系傷害額外提高」（效果值＝提高%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgStiffen</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僵化</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌐</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgStiffen</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>65</v>
+      </c>
+      <c r="M81">
+        <v>5</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P81">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超神進化【超重力場】：重力場扭曲造成的僵化。移動速度、攻速與造成的傷害同時下降（效果值＝三者共用的下降%）；比照【泥沼緩速】不吃控場遞減與韌性。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -5093,6 +5093,196 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgMireBleed</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">泥沼裂傷</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🩸</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dot</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skill</t>
+        </is>
+      </c>
+      <c r="I82">
+        <v>150</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>5</v>
+      </c>
+      <c r="N82">
+        <v>0.5</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strongest</t>
+        </is>
+      </c>
+      <c r="P82">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傳奇特效【侵蝕】：泥沼術附加的流血；每跳量與間隔由特效參數決定（引擎以 dps 覆寫）。比照【穿心裂血】採「取高並重新計時」，因此每一拍重塗不會把剩餘時間鎖死在滿值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgPlague</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">惡疫</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🦠</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poison</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skill</t>
+        </is>
+      </c>
+      <c r="I83">
+        <v>200</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>8</v>
+      </c>
+      <c r="N83">
+        <v>0.35</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strongest</t>
+        </is>
+      </c>
+      <c r="P83">
+        <v>1</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超神進化【惡疫魔沼】：沼澤塗上的毒性持續傷害；每跳量與間隔由超神進化參數決定（引擎以 dps 覆寫）。與泥沼的其他狀態不同，離開沼澤後仍會走完自己的持續時間，因此不採「只給兩跳」的重塗規則。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgInferno</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火獄烙印</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌋</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgInferno</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84">
+        <v>8</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P84">
+        <v>1</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超神進化【深淵火獄】：敵人的屬性標籤強制改為火屬性（效果值本身沒有意義，比照【地爆天星】只是一個計時容器）。屬性改寫走 skill2ForcedAttr，與【寒冰逆轉】同一個掛點。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -5283,6 +5283,136 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgSuperconduct</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超導電荷</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔋</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgSuperconduct</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>2</v>
+      </c>
+      <c r="M85">
+        <v>99999</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stack</t>
+        </is>
+      </c>
+      <c r="P85">
+        <v>100</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超神進化【永恒超導體】：閃電鏈每經過自身 1 次疊 1 層，每層使你的雷電傷害提高（效果值＝單層% × 層數）；設計未寫持續時間，比照【戰神屠錄】採「持續到死亡為止」，因此持續時間給一個單場戰鬥不可能走完的值，實際回收靠死亡時的 resetSkill2RT。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgThunderQuake</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">震雷</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚡</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgThunderQuake</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>25</v>
+      </c>
+      <c r="M86">
+        <v>8</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P86">
+        <v>1</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傳奇特效【震雷】：被落雷術擊中留下的雷痕（效果值＝該敵人「暈眩中」時受到的傷害提高%）。只有同時暈眩中才會吃到增傷，因此持續時間只要蓋得住一次落雷的暈眩即可。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -5413,6 +5413,71 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgWaterPrison</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">水牢</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌊</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgWaterPrison</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>100</v>
+      </c>
+      <c r="M87">
+        <v>6</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P87">
+        <v>1</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">超神進化【水牢天瀑】：被關進水牢的敵人（效果值＝受到的傷害提高%）。攻擊力下降那一半沿用既有的【攻擊】減益 atkDown，不另建一筆。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">新版技能【寒霜狀態】的層數與緩速：每疊 1 層使移動與攻擊速度各下降（效果值＝單層下降% × 層數），疊滿層數時凍結。比照泥沼緩速為場域型重塗，緩速本身不吃控場遞減與韌性。</t>
+          <t xml:space="preserve">新版技能【寒霜狀態】的層數與緩速：每疊 1 層使移動速度下降（效果值＝單層下降% × 層數），攻速倍率則為（1 − 單層下降%）^層數，疊滿層數時凍結。比照泥沼緩速為場域型重塗，緩速本身不吃控場遞減與韌性。</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t xml:space="preserve">新版技能【寒霜狀態】的寒冰持續傷害；每跳量占施放群組的本體技能傷害（引擎以 dps 覆寫）。依使用者決策，傷害不隨寒霜層數提高。</t>
+          <t xml:space="preserve">新版技能【寒霜狀態】的寒冰持續傷害；每跳量＝施放群組本體傷害 B × 寒霜共用倍率 ×（50×目前寒霜總層數＋該來源寒霜階每級增量×該階等級）%，總層數包含所有技能來源（引擎以 dps 覆寫）。</t>
         </is>
       </c>
     </row>
@@ -3525,11 +3525,11 @@
         </is>
       </c>
       <c r="P56">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t xml:space="preserve">新版技能【風切狀態】的減益本體：移動速度下降（效果值＝單層下降%，不隨層數再加深）且命中率下降；層數只影響風切割裂的每跳傷害，當下允許的層數上限由真空斬【無限風切】決定。</t>
+          <t xml:space="preserve">新版技能【風切狀態】的減益本體：移動速度下降（效果值＝單層下降%，不隨層數再加深）且命中率下降；層數只影響風切割裂的每跳傷害，當下允許的層數上限由真空斬【無限風切】與傳奇【裂痕】決定（表上的上限只是天花板）。</t>
         </is>
       </c>
     </row>
@@ -5475,6 +5475,71 @@
       <c r="Q87" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【水牢天瀑】：被關進水牢的敵人（效果值＝受到的傷害提高%）。攻擊力下降那一半沿用既有的【攻擊】減益 atkDown，不另建一筆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgWindErode</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風蝕</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌬️</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debuff</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stat</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sgWindErode</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>25</v>
+      </c>
+      <c r="M88">
+        <v>4</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">refresh</t>
+        </is>
+      </c>
+      <c r="P88">
+        <v>1</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傳奇特效【風蝕】：被風刃擊中留下的風蝕（效果值＝受到的傷害提高%）。沒有附加條件，狀態在身上就算數，走 skill2VulnACfg 的同一個 totalDmgPct。</t>
         </is>
       </c>
     </row>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -94,6 +94,21 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t xml:space="preserve">施加特效</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">持續特效</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作用特效</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t xml:space="preserve">說明</t>
         </is>
       </c>
@@ -152,7 +167,7 @@
       <c r="P2">
         <v>1</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t xml:space="preserve">傷口持續失血，每次作用造成技能傷害的一部分。</t>
         </is>
@@ -217,7 +232,7 @@
       <c r="P3">
         <v>1</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t xml:space="preserve">火焰持續灼燒，每次作用造成火屬性傷害。</t>
         </is>
@@ -282,7 +297,7 @@
       <c r="P4">
         <v>1</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t xml:space="preserve">毒素侵蝕血脈，每次作用造成毒屬性傷害。</t>
         </is>
@@ -347,7 +362,7 @@
       <c r="P5">
         <v>1</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t xml:space="preserve">暗影侵蝕軀體，每次作用造成暗屬性傷害。</t>
         </is>
@@ -412,7 +427,7 @@
       <c r="P6">
         <v>1</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t xml:space="preserve">疫病蔓延，每次作用造成毒屬性傷害。</t>
         </is>
@@ -482,7 +497,7 @@
       <c r="P7">
         <v>1</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t xml:space="preserve">每次作用造成目標最大生命一定比例的傷害，總量受施法者魔攻上限限制。</t>
         </is>
@@ -542,7 +557,7 @@
       <c r="P8">
         <v>1</v>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t xml:space="preserve">無法行動；持續時間受控場遞減與韌性影響。</t>
         </is>
@@ -602,7 +617,7 @@
       <c r="P9">
         <v>1</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t xml:space="preserve">攻擊速度下降；持續時間受控場遞減與韌性影響。</t>
         </is>
@@ -662,7 +677,7 @@
       <c r="P10">
         <v>1</v>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t xml:space="preserve">免疫一切傷害與負面狀態。</t>
         </is>
@@ -727,7 +742,7 @@
       <c r="P11">
         <v>1</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t xml:space="preserve">每秒回復最大生命的一定比例。</t>
         </is>
@@ -792,7 +807,7 @@
       <c r="P12">
         <v>1</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t xml:space="preserve">吸收傷害的屏障，占施法者最大生命一定比例；被打完或時間到就消失（時間到時未用完的部分一併消失）。</t>
         </is>
@@ -852,7 +867,7 @@
       <c r="P13">
         <v>1</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t xml:space="preserve">攻擊力提高。</t>
         </is>
@@ -912,7 +927,7 @@
       <c r="P14">
         <v>1</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t xml:space="preserve">防禦力提高。</t>
         </is>
@@ -972,7 +987,7 @@
       <c r="P15">
         <v>1</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t xml:space="preserve">攻擊速度提高。</t>
         </is>
@@ -1032,7 +1047,7 @@
       <c r="P16">
         <v>1</v>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t xml:space="preserve">閃避提高。</t>
         </is>
@@ -1092,7 +1107,7 @@
       <c r="P17">
         <v>1</v>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t xml:space="preserve">爆擊傷害提高。</t>
         </is>
@@ -1152,7 +1167,7 @@
       <c r="P18">
         <v>1</v>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t xml:space="preserve">格擋率提高。</t>
         </is>
@@ -1212,7 +1227,7 @@
       <c r="P19">
         <v>1</v>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t xml:space="preserve">反震傷害提高。</t>
         </is>
@@ -1272,7 +1287,7 @@
       <c r="P20">
         <v>1</v>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t xml:space="preserve">掉寶率提高。</t>
         </is>
@@ -1332,7 +1347,7 @@
       <c r="P21">
         <v>1</v>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t xml:space="preserve">物理與魔法穿透提高。</t>
         </is>
@@ -1392,7 +1407,7 @@
       <c r="P22">
         <v>1</v>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t xml:space="preserve">潛力【時空凝滯】：所有傷害提高。</t>
         </is>
@@ -1452,7 +1467,7 @@
       <c r="P23">
         <v>1</v>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t xml:space="preserve">潛力【極速之力】：攻速提高。</t>
         </is>
@@ -1517,7 +1532,7 @@
       <c r="P24">
         <v>1</v>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t xml:space="preserve">潛力【雷霆過載】：雷電傷害提高。</t>
         </is>
@@ -1577,7 +1592,7 @@
       <c r="P25">
         <v>1</v>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t xml:space="preserve">潛力【時間坍縮】：冷卻縮減。</t>
         </is>
@@ -1642,7 +1657,7 @@
       <c r="P26">
         <v>1</v>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t xml:space="preserve">潛力【聖療逆轉】：回復與溢傷轉換。</t>
         </is>
@@ -1707,7 +1722,7 @@
       <c r="P27">
         <v>1</v>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t xml:space="preserve">傳奇特效：暗屬性傷害提高。</t>
         </is>
@@ -1767,7 +1782,7 @@
       <c r="P28">
         <v>1</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t xml:space="preserve">傳奇特效：受到的傷害降低。</t>
         </is>
@@ -1832,7 +1847,7 @@
       <c r="P29">
         <v>1</v>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t xml:space="preserve">傳奇特效：受到的傷害降低。</t>
         </is>
@@ -1892,7 +1907,7 @@
       <c r="P30">
         <v>1</v>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t xml:space="preserve">目標攻擊力下降。</t>
         </is>
@@ -1952,7 +1967,7 @@
       <c r="P31">
         <v>1</v>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t xml:space="preserve">目標防禦力下降（舊存檔融合技快照相容保留，新設計改用穿透提升）。</t>
         </is>
@@ -2012,7 +2027,7 @@
       <c r="P32">
         <v>1</v>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t xml:space="preserve">潛力【時間結界】：目標攻擊速度下降。</t>
         </is>
@@ -2072,7 +2087,7 @@
       <c r="P33">
         <v>1</v>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【血刃斬】：每次作用造成技能傷害一定比例的傷害；每跳量與間隔由技能各階決定（引擎以 dps 覆寫）。</t>
         </is>
@@ -2137,7 +2152,7 @@
       <c r="P34">
         <v>1</v>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【血毒刃】：毒屬性持續傷害；每跳量與間隔由技能各階決定（引擎以 dps 覆寫）。</t>
         </is>
@@ -2197,7 +2212,7 @@
       <c r="P35">
         <v>1</v>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【鐵血之舞】：占最大生命比例的流血；自身流血直接扣生命、不吃護盾。</t>
         </is>
@@ -2257,7 +2272,7 @@
       <c r="P36">
         <v>1</v>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【狂風斬】：攻速額外提高（突破攻速上限、與自身攻速相乘）。</t>
         </is>
@@ -2317,7 +2332,7 @@
       <c r="P37">
         <v>1</v>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【狂暴之舞】：爆擊率提高。</t>
         </is>
@@ -2377,7 +2392,7 @@
       <c r="P38">
         <v>1</v>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【狂暴之舞】：爆擊傷害提高。</t>
         </is>
@@ -2437,7 +2452,7 @@
       <c r="P39">
         <v>1</v>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【暴風之舞】：化身暴風，期間自動施放雙刀亂舞、無法普攻。</t>
         </is>
@@ -2497,7 +2512,7 @@
       <c r="P40">
         <v>1</v>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【嗜血狂怒】：攻速乘算提高（突破攻速上限）；期間各階狂怒效果生效。</t>
         </is>
@@ -2557,7 +2572,7 @@
       <c r="P41">
         <v>4</v>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【破甲擊】：防禦降低（可疊層，疊層時重置時間；獨立鍵、與舊 defDown 減益加總計算）。</t>
         </is>
@@ -2622,7 +2637,7 @@
       <c r="P42">
         <v>1</v>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【火球術／火柱】：火屬性持續傷害；每跳量與間隔由技能各階決定（引擎以 dps 覆寫）。</t>
         </is>
@@ -2687,7 +2702,7 @@
       <c r="P43">
         <v>1</v>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【火焰增幅】：火屬性傷害提升（層數由引擎累加成單一數值，故用後蓋前並重置時間）。</t>
         </is>
@@ -2752,7 +2767,7 @@
       <c r="P44">
         <v>1</v>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【火狩】：火狩環繞自身的剩餘時間；【再生】的擊殺延長會累加在這裡。</t>
         </is>
@@ -2817,7 +2832,7 @@
       <c r="P45">
         <v>1</v>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【岩甲術】：岩甲護盾的剩餘時間；第 3、5、6、7 階的效果只在此期間生效（護盾本身走「護盾」狀態）。</t>
         </is>
@@ -2877,7 +2892,7 @@
       <c r="P46">
         <v>1</v>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【岩甲增幅】：損失護盾換得的傷害增幅（層數由引擎累加成單一數值，故用後蓋前並重置時間）。</t>
         </is>
@@ -2942,7 +2957,7 @@
       <c r="P47">
         <v>1</v>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【泥沼術】：攻速與移動速度下降（效果值＝攻速下降%）。同類型緩速依「取代」規則後蓋前並重新計時；為場域型持續重塗，不吃控場遞減與韌性。</t>
         </is>
@@ -3007,7 +3022,7 @@
       <c r="P48">
         <v>1</v>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【毒沼術】：毒性持續傷害；每跳量與間隔由技能各階決定（引擎以 dps 覆寫），站在沼澤中才會被重塗。</t>
         </is>
@@ -3072,7 +3087,7 @@
       <c r="P49">
         <v>1</v>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【熔岩沼】：火焰持續傷害；每跳量與間隔由技能各階決定（引擎以 dps 覆寫），站在岩漿中才會被重塗。</t>
         </is>
@@ -3137,7 +3152,7 @@
       <c r="P50">
         <v>1</v>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【環體電球】：電球環繞自身的剩餘時間（與火狩各自一格，兩者互不覆蓋）。</t>
         </is>
@@ -3202,7 +3217,7 @@
       <c r="P51">
         <v>5</v>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【寒霜狀態】的層數與緩速：每疊 1 層使移動速度下降（效果值＝單層下降% × 層數），攻速倍率則為（1 − 單層下降%）^層數，疊滿層數時凍結。比照泥沼緩速為場域型重塗，緩速本身不吃控場遞減與韌性。</t>
         </is>
@@ -3267,7 +3282,7 @@
       <c r="P52">
         <v>1</v>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【寒霜狀態】的寒冰持續傷害；每跳量＝施放群組本體傷害 B × 寒霜共用倍率 ×（50×目前寒霜總層數＋該來源寒霜階每級增量×該階等級）%，總層數包含所有技能來源（引擎以 dps 覆寫）。</t>
         </is>
@@ -3332,7 +3347,7 @@
       <c r="P53">
         <v>1</v>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【寒霜狀態】疊滿層數的凍結標記。行動限制本身由「暈眩」承擔（因此完整沿用 BOSS 控場免疫、韌性折減與控場遞減），本狀態只標記「正在凍結中」，供【水龍捲】增傷與【寒冰爆裂箭】判定冰爆時機。</t>
         </is>
@@ -3397,7 +3412,7 @@
       <c r="P54">
         <v>1</v>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【寒冰逆轉】：敵人的屬性標籤強制改為寒冰，且受到的寒冰傷害提高（效果值＝提高%）。</t>
         </is>
@@ -3462,7 +3477,7 @@
       <c r="P55">
         <v>1</v>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【冰霜新星】：施放後 6 秒內，攻擊你的敵人有 25% 機率被附加寒霜狀態。</t>
         </is>
@@ -3527,7 +3542,7 @@
       <c r="P56">
         <v>6</v>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【風切狀態】的減益本體：移動速度下降（效果值＝單層下降%，不隨層數再加深）且命中率下降；層數只影響風切割裂的每跳傷害，當下允許的層數上限由真空斬【無限風切】與傳奇【裂痕】決定（表上的上限只是天花板）。</t>
         </is>
@@ -3592,7 +3607,7 @@
       <c r="P57">
         <v>1</v>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【風切狀態】的風系持續傷害；每跳量占施放群組的本體技能傷害並隨風切層數提高（引擎以 dps 覆寫）。</t>
         </is>
@@ -3657,7 +3672,7 @@
       <c r="P58">
         <v>1</v>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【狂風碎裂】：被風刃命中的敵人移動速度下降（效果值＝下降%）。同類型緩速依「取代」規則後蓋前並重新計時。</t>
         </is>
@@ -3722,7 +3737,7 @@
       <c r="P59">
         <v>1</v>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【暴風屏障】：屏障的剩餘時間與傷害減免（效果值＝減免%）；第 2～6 階的效果只在此期間生效（護盾由節拍逐次給予）。</t>
         </is>
@@ -3787,7 +3802,7 @@
       <c r="P60">
         <v>1</v>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【虛空斬】：虛空斬擊還會在場上繞行多久（環繞場域的剩餘時間投影，比照火狩）。</t>
         </is>
@@ -3852,7 +3867,7 @@
       <c r="P61">
         <v>1</v>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t xml:space="preserve">新版技能【暴風神體】：風暴之神附體期間的傷害減免（效果值＝減免%），且風系傷害額外乘算提高。與暴風屏障是分開的兩個狀態。</t>
         </is>
@@ -3912,7 +3927,7 @@
       <c r="P62">
         <v>10</v>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t xml:space="preserve">傳奇特效【千瘡百孔】：每次突刺命中疊 1 層，每層使該敵人受到的傷害提高（效果值＝單層提高%）；層數上限由特效參數決定。</t>
         </is>
@@ -3977,7 +3992,7 @@
       <c r="P63">
         <v>100</v>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【暗影絕殺者】：每次突刺命中疊 1 層，每層使該敵人受到的傷害提高（效果值＝單層提高%）；層數上限與單層值由技能參數決定。</t>
         </is>
@@ -4037,7 +4052,7 @@
       <c r="P64">
         <v>1</v>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t xml:space="preserve">傳奇特效【穿心裂血】：突刺附加的流血；每跳量與間隔由特效參數決定（引擎以 dps 覆寫）。</t>
         </is>
@@ -4097,7 +4112,7 @@
       <c r="P65">
         <v>1</v>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【幻影八方陣】：期間有一定機率絕對閃避敵方攻擊（效果值＝機率%）；此擲骰與命中率無關，先於命中判定結算。</t>
         </is>
@@ -4157,7 +4172,7 @@
       <c r="P66">
         <v>20</v>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【死亡收割者】：飛刀每殺死 1 個敵人疊 1 層，每層使你造成的所有傷害提高（效果值＝單層提高%）；層數上限與單層值由技能參數決定。</t>
         </is>
@@ -4217,7 +4232,7 @@
       <c r="P67">
         <v>1</v>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t xml:space="preserve">傳奇特效【輪舞刃】：繞行在你周圍的飛刀還會留在場上多久（環繞場域的剩餘時間投影，比照火狩）。</t>
         </is>
@@ -4277,7 +4292,7 @@
       <c r="P68">
         <v>100</v>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【殺神領域】：領域內的敵人死亡時疊 1 層，每層使你造成的所有傷害提高（效果值＝單層% × 層數）。</t>
         </is>
@@ -4342,7 +4357,7 @@
       <c r="P69">
         <v>10</v>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【萬毒血霧】：領域內每次作用疊 1 層，每跳量＝單層量 × 層數（引擎以 dps 覆寫）。</t>
         </is>
@@ -4407,7 +4422,7 @@
       <c r="P70">
         <v>20</v>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【火之神樂】：雙刀亂舞每命中 1 次疊 1 層，每跳量＝單層量 × 層數（引擎以 dps 覆寫）。</t>
         </is>
@@ -4467,7 +4482,7 @@
       <c r="P71">
         <v>1</v>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t xml:space="preserve">傳奇【不屈之誓】：死亡延後生效的期間，你造成的所有傷害提高。</t>
         </is>
@@ -4527,7 +4542,7 @@
       <c r="P72">
         <v>1</v>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t xml:space="preserve">傳奇【血霧】：站在血霧裡的標記，受傷時回復施放者生命。效果值＝血霧生成當下定版的回復比例%（沒有任何屬性讀這個鍵，它只是把數值帶在標記上）。</t>
         </is>
@@ -4587,7 +4602,7 @@
       <c r="P73">
         <v>1</v>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t xml:space="preserve">傳奇【怒火】：反擊累積達門檻時獲得，期間你造成的所有傷害提高。</t>
         </is>
@@ -4647,7 +4662,7 @@
       <c r="P74">
         <v>50</v>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t xml:space="preserve">傳奇【燃血】：【血飲術】每造成 1 次自身生命損失疊 1 層，每層使你造成的所有傷害提高（效果值＝單層% × 層數）。</t>
         </is>
@@ -4707,7 +4722,7 @@
       <c r="P75">
         <v>10</v>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t xml:space="preserve">傳奇【屠戮者】：狂怒期間每擊殺 1 個敵人疊 1 層，每層使【嗜血反震】的效果提高（效果值＝單層% × 層數）。</t>
         </is>
@@ -4767,7 +4782,7 @@
       <c r="P76">
         <v>100</v>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【戰神屠錄】：狂怒期間每擊殺 1 個敵人疊 1 層，每層使你造成的所有傷害提高（效果值＝單層% × 層數）；設計為「持續到死亡為止」，因此持續時間給一個單場戰鬥不可能走完的值，實際回收靠死亡時的 resetSkill2RT。</t>
         </is>
@@ -4827,7 +4842,7 @@
       <c r="P77">
         <v>1</v>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【阿修羅霸王拳】：每隔一段時間自動發動，短暫期間內你造成的所有傷害大幅提高。</t>
         </is>
@@ -4892,7 +4907,7 @@
       <c r="P78">
         <v>1</v>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【地爆天星】：距離下一顆超巨型殞石落下還有多久（剩餘時間即倒數，效果值本身沒有意義；比照【暴風化身】【火狩】的純計時狀態）。</t>
         </is>
@@ -4957,7 +4972,7 @@
       <c r="P79">
         <v>1</v>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t xml:space="preserve">傳奇特效【爆燃】：火龍捲每造成 1 段傷害就疊 1 層，使該敵人受到的燃燒傷害提高（效果值＝目前的總提高%）。設計文檔未設層數上限，因此比照【火焰增幅】由引擎累加成單一數值後「後蓋前」，不使用狀態表的疊層規則。</t>
         </is>
@@ -5022,7 +5037,7 @@
       <c r="P80">
         <v>1</v>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【超重岩之術】：被壓縮的巨岩之力封住的敵人。行動限制本身由「暈眩」承擔（因此完整沿用 BOSS 控場免疫、韌性折減與控場遞減），本狀態只負責「受到的土系傷害額外提高」（效果值＝提高%）。</t>
         </is>
@@ -5087,7 +5102,7 @@
       <c r="P81">
         <v>1</v>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【超重力場】：重力場扭曲造成的僵化。移動速度、攻速與造成的傷害同時下降（效果值＝三者共用的下降%）；比照【泥沼緩速】不吃控場遞減與韌性。</t>
         </is>
@@ -5147,7 +5162,7 @@
       <c r="P82">
         <v>1</v>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t xml:space="preserve">傳奇特效【侵蝕】：泥沼術附加的流血；每跳量與間隔由特效參數決定（引擎以 dps 覆寫）。比照【穿心裂血】採「取高並重新計時」，因此每一拍重塗不會把剩餘時間鎖死在滿值。</t>
         </is>
@@ -5212,7 +5227,7 @@
       <c r="P83">
         <v>1</v>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【惡疫魔沼】：沼澤塗上的毒性持續傷害；每跳量與間隔由超神進化參數決定（引擎以 dps 覆寫）。與泥沼的其他狀態不同，離開沼澤後仍會走完自己的持續時間，因此不採「只給兩跳」的重塗規則。</t>
         </is>
@@ -5277,7 +5292,7 @@
       <c r="P84">
         <v>1</v>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="T84" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【深淵火獄】：敵人的屬性標籤強制改為火屬性（效果值本身沒有意義，比照【地爆天星】只是一個計時容器）。屬性改寫走 skill2ForcedAttr，與【寒冰逆轉】同一個掛點。</t>
         </is>
@@ -5342,7 +5357,7 @@
       <c r="P85">
         <v>100</v>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【永恒超導體】：閃電鏈每經過自身 1 次疊 1 層，每層使你的雷電傷害提高（效果值＝單層% × 層數）；設計未寫持續時間，比照【戰神屠錄】採「持續到死亡為止」，因此持續時間給一個單場戰鬥不可能走完的值，實際回收靠死亡時的 resetSkill2RT。</t>
         </is>
@@ -5407,7 +5422,7 @@
       <c r="P86">
         <v>1</v>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t xml:space="preserve">傳奇特效【震雷】：被落雷術擊中留下的雷痕（效果值＝該敵人「暈眩中」時受到的傷害提高%）。只有同時暈眩中才會吃到增傷，因此持續時間只要蓋得住一次落雷的暈眩即可。</t>
         </is>
@@ -5472,7 +5487,7 @@
       <c r="P87">
         <v>1</v>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="T87" t="inlineStr">
         <is>
           <t xml:space="preserve">超神進化【水牢天瀑】：被關進水牢的敵人（效果值＝受到的傷害提高%）。攻擊力下降那一半沿用既有的【攻擊】減益 atkDown，不另建一筆。</t>
         </is>
@@ -5537,7 +5552,7 @@
       <c r="P88">
         <v>1</v>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t xml:space="preserve">傳奇特效【風蝕】：被風刃擊中留下的風蝕（效果值＝受到的傷害提高%）。沒有附加條件，狀態在身上就算數，走 skill2VulnACfg 的同一個 totalDmgPct。</t>
         </is>
@@ -5969,6 +5984,49 @@
         </is>
       </c>
     </row>
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施加特效 / 持續特效 / 作用特效（2026-09-03 VFX Preset 化）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每一格填 VFX 編輯器存出來的 Preset 檔名（vfx/presets/&lt;檔名&gt;.json，不含 .json；含 .json 也接受）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施加特效＝狀態第一次出現在目標身上時播一次（重新計時／疊層不重播）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">持續特效＝狀態存在期間掛在目標身上循環播放的特效（Preset 應設 loop；原點＝腳底、身高約 60px）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作用特效＝持續傷害每跳一次播一次（只對 dot 有意義；同一拍多個敵人會合併成一則事件）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">留白＝該狀態沒有那一段畫面；純計時用的內部狀態（如火狩剩餘時間）建議三欄都留白，畫面交給技能本身。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>